--- a/evals/datasets/test_dataset.xlsx
+++ b/evals/datasets/test_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Samuel\Projects\Skripsi\TravelPlanner\TravelPlannerLLMRAGMCP\evals\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FB692A-FEFF-400D-86AE-C8B915F97BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD982EE-369E-4172-99C5-933B53C13F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{303DDD28-EEF9-48CD-845F-90282090C77A}"/>
   </bookViews>
@@ -549,10 +549,10 @@
         <v>25</v>
       </c>
       <c r="F5" s="1">
-        <v>45910</v>
+        <v>46275</v>
       </c>
       <c r="G5" s="1">
-        <v>45915</v>
+        <v>46280</v>
       </c>
       <c r="H5" t="s">
         <v>21</v>
@@ -569,10 +569,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="1">
-        <v>45910</v>
+        <v>46275</v>
       </c>
       <c r="G6" s="1">
-        <v>45915</v>
+        <v>46280</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
